--- a/public/examples/excel-rule-engine-example.xlsx
+++ b/public/examples/excel-rule-engine-example.xlsx
@@ -647,7 +647,15 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F233"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="60.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -670,168 +678,4648 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2">
         <v>18.99</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2">
         <v>0.3</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E2">
         <v>5.65</v>
       </c>
       <c r="F2" t="str">
-        <v>售价 0-18.99 且重量 0-0.3kg</v>
+        <v>售价R$0-R$18.99, 重量0-0.3kg</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3">
         <v>19</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3">
         <v>48.99</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3">
         <v>0.3</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E3">
         <v>6.55</v>
       </c>
       <c r="F3" t="str">
-        <v>售价 19-48.99 且重量 0-0.3kg</v>
+        <v>售价R$19-R$48.99, 重量0-0.3kg</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4">
         <v>49</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B4">
         <v>78.99</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D4">
         <v>0.3</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E4">
         <v>7.75</v>
       </c>
       <c r="F4" t="str">
-        <v>售价 49-78.99 且重量 0-0.3kg</v>
+        <v>售价R$49-R$78.99, 重量0-0.3kg</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5">
         <v>79</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B5">
         <v>99.99</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D5">
         <v>0.3</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E5">
         <v>12.35</v>
       </c>
       <c r="F5" t="str">
-        <v>售价 79-99.99 且重量 0-0.3kg</v>
+        <v>售价R$79-R$99.99, 重量0-0.3kg</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6">
+        <v>100</v>
+      </c>
+      <c r="B6">
+        <v>119.99</v>
+      </c>
+      <c r="C6">
         <v>0</v>
       </c>
-      <c r="B6" t="str">
+      <c r="D6">
+        <v>0.3</v>
+      </c>
+      <c r="E6">
+        <v>14.35</v>
+      </c>
+      <c r="F6" t="str">
+        <v>售价R$100-R$119.99, 重量0-0.3kg</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>120</v>
+      </c>
+      <c r="B7">
+        <v>149.99</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0.3</v>
+      </c>
+      <c r="E7">
+        <v>16.45</v>
+      </c>
+      <c r="F7" t="str">
+        <v>售价R$120-R$149.99, 重量0-0.3kg</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>150</v>
+      </c>
+      <c r="B8">
+        <v>199.99</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0.3</v>
+      </c>
+      <c r="E8">
+        <v>18.45</v>
+      </c>
+      <c r="F8" t="str">
+        <v>售价R$150-R$199.99, 重量0-0.3kg</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>200</v>
+      </c>
+      <c r="B9">
+        <v>99999</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0.3</v>
+      </c>
+      <c r="E9">
+        <v>20.95</v>
+      </c>
+      <c r="F9" t="str">
+        <v>售价R$200-以上, 重量0-0.3kg</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10">
         <v>18.99</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C10">
         <v>0.3</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D10">
         <v>0.5</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E10">
         <v>5.95</v>
       </c>
-      <c r="F6" t="str">
-        <v>售价 0-18.99 且重量 0.3-0.5kg</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
+      <c r="F10" t="str">
+        <v>售价R$0-R$18.99, 重量0.3-0.5kg</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
         <v>19</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B11">
         <v>48.99</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C11">
         <v>0.3</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D11">
         <v>0.5</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E11">
         <v>6.65</v>
       </c>
-      <c r="F7" t="str">
-        <v>售价 19-48.99 且重量 0.3-0.5kg</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
+      <c r="F11" t="str">
+        <v>售价R$19-R$48.99, 重量0.3-0.5kg</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
         <v>49</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B12">
         <v>78.99</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C12">
         <v>0.3</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D12">
         <v>0.5</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E12">
         <v>7.85</v>
       </c>
-      <c r="F8" t="str">
-        <v>售价 49-78.99 且重量 0.3-0.5kg</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
+      <c r="F12" t="str">
+        <v>售价R$49-R$78.99, 重量0.3-0.5kg</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
         <v>79</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B13">
         <v>99.99</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C13">
         <v>0.3</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D13">
         <v>0.5</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E13">
         <v>13.25</v>
       </c>
-      <c r="F9" t="str">
-        <v>售价 79-99.99 且重量 0.3-0.5kg</v>
+      <c r="F13" t="str">
+        <v>售价R$79-R$99.99, 重量0.3-0.5kg</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>100</v>
+      </c>
+      <c r="B14">
+        <v>119.99</v>
+      </c>
+      <c r="C14">
+        <v>0.3</v>
+      </c>
+      <c r="D14">
+        <v>0.5</v>
+      </c>
+      <c r="E14">
+        <v>15.45</v>
+      </c>
+      <c r="F14" t="str">
+        <v>售价R$100-R$119.99, 重量0.3-0.5kg</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>120</v>
+      </c>
+      <c r="B15">
+        <v>149.99</v>
+      </c>
+      <c r="C15">
+        <v>0.3</v>
+      </c>
+      <c r="D15">
+        <v>0.5</v>
+      </c>
+      <c r="E15">
+        <v>17.65</v>
+      </c>
+      <c r="F15" t="str">
+        <v>售价R$120-R$149.99, 重量0.3-0.5kg</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>150</v>
+      </c>
+      <c r="B16">
+        <v>199.99</v>
+      </c>
+      <c r="C16">
+        <v>0.3</v>
+      </c>
+      <c r="D16">
+        <v>0.5</v>
+      </c>
+      <c r="E16">
+        <v>19.85</v>
+      </c>
+      <c r="F16" t="str">
+        <v>售价R$150-R$199.99, 重量0.3-0.5kg</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>200</v>
+      </c>
+      <c r="B17">
+        <v>99999</v>
+      </c>
+      <c r="C17">
+        <v>0.3</v>
+      </c>
+      <c r="D17">
+        <v>0.5</v>
+      </c>
+      <c r="E17">
+        <v>22.55</v>
+      </c>
+      <c r="F17" t="str">
+        <v>售价R$200-以上, 重量0.3-0.5kg</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18">
+        <v>18.99</v>
+      </c>
+      <c r="C18">
+        <v>0.5</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>6.05</v>
+      </c>
+      <c r="F18" t="str">
+        <v>售价R$0-R$18.99, 重量0.5-1kg</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>48.99</v>
+      </c>
+      <c r="C19">
+        <v>0.5</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>6.75</v>
+      </c>
+      <c r="F19" t="str">
+        <v>售价R$19-R$48.99, 重量0.5-1kg</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>49</v>
+      </c>
+      <c r="B20">
+        <v>78.99</v>
+      </c>
+      <c r="C20">
+        <v>0.5</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>7.95</v>
+      </c>
+      <c r="F20" t="str">
+        <v>售价R$49-R$78.99, 重量0.5-1kg</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>79</v>
+      </c>
+      <c r="B21">
+        <v>99.99</v>
+      </c>
+      <c r="C21">
+        <v>0.5</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>13.85</v>
+      </c>
+      <c r="F21" t="str">
+        <v>售价R$79-R$99.99, 重量0.5-1kg</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>100</v>
+      </c>
+      <c r="B22">
+        <v>119.99</v>
+      </c>
+      <c r="C22">
+        <v>0.5</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>16.15</v>
+      </c>
+      <c r="F22" t="str">
+        <v>售价R$100-R$119.99, 重量0.5-1kg</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>120</v>
+      </c>
+      <c r="B23">
+        <v>149.99</v>
+      </c>
+      <c r="C23">
+        <v>0.5</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>18.45</v>
+      </c>
+      <c r="F23" t="str">
+        <v>售价R$120-R$149.99, 重量0.5-1kg</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>150</v>
+      </c>
+      <c r="B24">
+        <v>199.99</v>
+      </c>
+      <c r="C24">
+        <v>0.5</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>20.75</v>
+      </c>
+      <c r="F24" t="str">
+        <v>售价R$150-R$199.99, 重量0.5-1kg</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>200</v>
+      </c>
+      <c r="B25">
+        <v>99999</v>
+      </c>
+      <c r="C25">
+        <v>0.5</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>23.65</v>
+      </c>
+      <c r="F25" t="str">
+        <v>售价R$200-以上, 重量0.5-1kg</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26">
+        <v>18.99</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1.5</v>
+      </c>
+      <c r="E26">
+        <v>6.15</v>
+      </c>
+      <c r="F26" t="str">
+        <v>售价R$0-R$18.99, 重量1-1.5kg</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>19</v>
+      </c>
+      <c r="B27">
+        <v>48.99</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1.5</v>
+      </c>
+      <c r="E27">
+        <v>6.85</v>
+      </c>
+      <c r="F27" t="str">
+        <v>售价R$19-R$48.99, 重量1-1.5kg</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>49</v>
+      </c>
+      <c r="B28">
+        <v>78.99</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1.5</v>
+      </c>
+      <c r="E28">
+        <v>8.05</v>
+      </c>
+      <c r="F28" t="str">
+        <v>售价R$49-R$78.99, 重量1-1.5kg</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>79</v>
+      </c>
+      <c r="B29">
+        <v>99.99</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1.5</v>
+      </c>
+      <c r="E29">
+        <v>14.15</v>
+      </c>
+      <c r="F29" t="str">
+        <v>售价R$79-R$99.99, 重量1-1.5kg</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>100</v>
+      </c>
+      <c r="B30">
+        <v>119.99</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1.5</v>
+      </c>
+      <c r="E30">
+        <v>16.45</v>
+      </c>
+      <c r="F30" t="str">
+        <v>售价R$100-R$119.99, 重量1-1.5kg</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>120</v>
+      </c>
+      <c r="B31">
+        <v>149.99</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1.5</v>
+      </c>
+      <c r="E31">
+        <v>18.85</v>
+      </c>
+      <c r="F31" t="str">
+        <v>售价R$120-R$149.99, 重量1-1.5kg</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>150</v>
+      </c>
+      <c r="B32">
+        <v>199.99</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1.5</v>
+      </c>
+      <c r="E32">
+        <v>21.15</v>
+      </c>
+      <c r="F32" t="str">
+        <v>售价R$150-R$199.99, 重量1-1.5kg</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>200</v>
+      </c>
+      <c r="B33">
+        <v>99999</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1.5</v>
+      </c>
+      <c r="E33">
+        <v>24.65</v>
+      </c>
+      <c r="F33" t="str">
+        <v>售价R$200-以上, 重量1-1.5kg</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34">
+        <v>18.99</v>
+      </c>
+      <c r="C34">
+        <v>1.5</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>6.25</v>
+      </c>
+      <c r="F34" t="str">
+        <v>售价R$0-R$18.99, 重量1.5-2kg</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>19</v>
+      </c>
+      <c r="B35">
+        <v>48.99</v>
+      </c>
+      <c r="C35">
+        <v>1.5</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35">
+        <v>6.95</v>
+      </c>
+      <c r="F35" t="str">
+        <v>售价R$19-R$48.99, 重量1.5-2kg</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>49</v>
+      </c>
+      <c r="B36">
+        <v>78.99</v>
+      </c>
+      <c r="C36">
+        <v>1.5</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>8.15</v>
+      </c>
+      <c r="F36" t="str">
+        <v>售价R$49-R$78.99, 重量1.5-2kg</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>79</v>
+      </c>
+      <c r="B37">
+        <v>99.99</v>
+      </c>
+      <c r="C37">
+        <v>1.5</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>14.45</v>
+      </c>
+      <c r="F37" t="str">
+        <v>售价R$79-R$99.99, 重量1.5-2kg</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>100</v>
+      </c>
+      <c r="B38">
+        <v>119.99</v>
+      </c>
+      <c r="C38">
+        <v>1.5</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38">
+        <v>16.85</v>
+      </c>
+      <c r="F38" t="str">
+        <v>售价R$100-R$119.99, 重量1.5-2kg</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>120</v>
+      </c>
+      <c r="B39">
+        <v>149.99</v>
+      </c>
+      <c r="C39">
+        <v>1.5</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>19.25</v>
+      </c>
+      <c r="F39" t="str">
+        <v>售价R$120-R$149.99, 重量1.5-2kg</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>150</v>
+      </c>
+      <c r="B40">
+        <v>199.99</v>
+      </c>
+      <c r="C40">
+        <v>1.5</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>21.65</v>
+      </c>
+      <c r="F40" t="str">
+        <v>售价R$150-R$199.99, 重量1.5-2kg</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>200</v>
+      </c>
+      <c r="B41">
+        <v>99999</v>
+      </c>
+      <c r="C41">
+        <v>1.5</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41">
+        <v>24.65</v>
+      </c>
+      <c r="F41" t="str">
+        <v>售价R$200-以上, 重量1.5-2kg</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42">
+        <v>18.99</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42">
+        <v>6.35</v>
+      </c>
+      <c r="F42" t="str">
+        <v>售价R$0-R$18.99, 重量2-3kg</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>19</v>
+      </c>
+      <c r="B43">
+        <v>48.99</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43">
+        <v>7.95</v>
+      </c>
+      <c r="F43" t="str">
+        <v>售价R$19-R$48.99, 重量2-3kg</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>49</v>
+      </c>
+      <c r="B44">
+        <v>78.99</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+      <c r="E44">
+        <v>8.55</v>
+      </c>
+      <c r="F44" t="str">
+        <v>售价R$49-R$78.99, 重量2-3kg</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>79</v>
+      </c>
+      <c r="B45">
+        <v>99.99</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45">
+        <v>15.75</v>
+      </c>
+      <c r="F45" t="str">
+        <v>售价R$79-R$99.99, 重量2-3kg</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>100</v>
+      </c>
+      <c r="B46">
+        <v>119.99</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46">
+        <v>18.35</v>
+      </c>
+      <c r="F46" t="str">
+        <v>售价R$100-R$119.99, 重量2-3kg</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>120</v>
+      </c>
+      <c r="B47">
+        <v>149.99</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>21.05</v>
+      </c>
+      <c r="F47" t="str">
+        <v>售价R$120-R$149.99, 重量2-3kg</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>150</v>
+      </c>
+      <c r="B48">
+        <v>199.99</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
+        <v>23.65</v>
+      </c>
+      <c r="F48" t="str">
+        <v>售价R$150-R$199.99, 重量2-3kg</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>200</v>
+      </c>
+      <c r="B49">
+        <v>99999</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>26.25</v>
+      </c>
+      <c r="F49" t="str">
+        <v>售价R$200-以上, 重量2-3kg</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50">
+        <v>18.99</v>
+      </c>
+      <c r="C50">
+        <v>3</v>
+      </c>
+      <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50">
+        <v>6.45</v>
+      </c>
+      <c r="F50" t="str">
+        <v>售价R$0-R$18.99, 重量3-4kg</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>19</v>
+      </c>
+      <c r="B51">
+        <v>48.99</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51">
+        <v>4</v>
+      </c>
+      <c r="E51">
+        <v>8.15</v>
+      </c>
+      <c r="F51" t="str">
+        <v>售价R$19-R$48.99, 重量3-4kg</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52">
+        <v>78.99</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52">
+        <v>8.95</v>
+      </c>
+      <c r="F52" t="str">
+        <v>售价R$49-R$78.99, 重量3-4kg</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>79</v>
+      </c>
+      <c r="B53">
+        <v>99.99</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53">
+        <v>17.05</v>
+      </c>
+      <c r="F53" t="str">
+        <v>售价R$79-R$99.99, 重量3-4kg</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>100</v>
+      </c>
+      <c r="B54">
+        <v>119.99</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+      <c r="E54">
+        <v>19.85</v>
+      </c>
+      <c r="F54" t="str">
+        <v>售价R$100-R$119.99, 重量3-4kg</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>120</v>
+      </c>
+      <c r="B55">
+        <v>149.99</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55">
+        <v>22.65</v>
+      </c>
+      <c r="F55" t="str">
+        <v>售价R$120-R$149.99, 重量3-4kg</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>150</v>
+      </c>
+      <c r="B56">
+        <v>199.99</v>
+      </c>
+      <c r="C56">
+        <v>3</v>
+      </c>
+      <c r="D56">
+        <v>4</v>
+      </c>
+      <c r="E56">
+        <v>25.55</v>
+      </c>
+      <c r="F56" t="str">
+        <v>售价R$150-R$199.99, 重量3-4kg</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>200</v>
+      </c>
+      <c r="B57">
+        <v>99999</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57">
+        <v>4</v>
+      </c>
+      <c r="E57">
+        <v>28.35</v>
+      </c>
+      <c r="F57" t="str">
+        <v>售价R$200-以上, 重量3-4kg</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58">
+        <v>18.99</v>
+      </c>
+      <c r="C58">
+        <v>4</v>
+      </c>
+      <c r="D58">
+        <v>5</v>
+      </c>
+      <c r="E58">
+        <v>6.55</v>
+      </c>
+      <c r="F58" t="str">
+        <v>售价R$0-R$18.99, 重量4-5kg</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>19</v>
+      </c>
+      <c r="B59">
+        <v>48.99</v>
+      </c>
+      <c r="C59">
+        <v>4</v>
+      </c>
+      <c r="D59">
+        <v>5</v>
+      </c>
+      <c r="E59">
+        <v>8.35</v>
+      </c>
+      <c r="F59" t="str">
+        <v>售价R$19-R$48.99, 重量4-5kg</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>49</v>
+      </c>
+      <c r="B60">
+        <v>78.99</v>
+      </c>
+      <c r="C60">
+        <v>4</v>
+      </c>
+      <c r="D60">
+        <v>5</v>
+      </c>
+      <c r="E60">
+        <v>9.75</v>
+      </c>
+      <c r="F60" t="str">
+        <v>售价R$49-R$78.99, 重量4-5kg</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>79</v>
+      </c>
+      <c r="B61">
+        <v>99.99</v>
+      </c>
+      <c r="C61">
+        <v>4</v>
+      </c>
+      <c r="D61">
+        <v>5</v>
+      </c>
+      <c r="E61">
+        <v>18.45</v>
+      </c>
+      <c r="F61" t="str">
+        <v>售价R$79-R$99.99, 重量4-5kg</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>100</v>
+      </c>
+      <c r="B62">
+        <v>119.99</v>
+      </c>
+      <c r="C62">
+        <v>4</v>
+      </c>
+      <c r="D62">
+        <v>5</v>
+      </c>
+      <c r="E62">
+        <v>21.55</v>
+      </c>
+      <c r="F62" t="str">
+        <v>售价R$100-R$119.99, 重量4-5kg</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>120</v>
+      </c>
+      <c r="B63">
+        <v>149.99</v>
+      </c>
+      <c r="C63">
+        <v>4</v>
+      </c>
+      <c r="D63">
+        <v>5</v>
+      </c>
+      <c r="E63">
+        <v>24.65</v>
+      </c>
+      <c r="F63" t="str">
+        <v>售价R$120-R$149.99, 重量4-5kg</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>150</v>
+      </c>
+      <c r="B64">
+        <v>199.99</v>
+      </c>
+      <c r="C64">
+        <v>4</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+      <c r="E64">
+        <v>27.75</v>
+      </c>
+      <c r="F64" t="str">
+        <v>售价R$150-R$199.99, 重量4-5kg</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>200</v>
+      </c>
+      <c r="B65">
+        <v>99999</v>
+      </c>
+      <c r="C65">
+        <v>4</v>
+      </c>
+      <c r="D65">
+        <v>5</v>
+      </c>
+      <c r="E65">
+        <v>30.75</v>
+      </c>
+      <c r="F65" t="str">
+        <v>售价R$200-以上, 重量4-5kg</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0</v>
+      </c>
+      <c r="B66">
+        <v>18.99</v>
+      </c>
+      <c r="C66">
+        <v>5</v>
+      </c>
+      <c r="D66">
+        <v>6</v>
+      </c>
+      <c r="E66">
+        <v>6.65</v>
+      </c>
+      <c r="F66" t="str">
+        <v>售价R$0-R$18.99, 重量5-6kg</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>19</v>
+      </c>
+      <c r="B67">
+        <v>48.99</v>
+      </c>
+      <c r="C67">
+        <v>5</v>
+      </c>
+      <c r="D67">
+        <v>6</v>
+      </c>
+      <c r="E67">
+        <v>8.55</v>
+      </c>
+      <c r="F67" t="str">
+        <v>售价R$19-R$48.99, 重量5-6kg</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>49</v>
+      </c>
+      <c r="B68">
+        <v>78.99</v>
+      </c>
+      <c r="C68">
+        <v>5</v>
+      </c>
+      <c r="D68">
+        <v>6</v>
+      </c>
+      <c r="E68">
+        <v>9.95</v>
+      </c>
+      <c r="F68" t="str">
+        <v>售价R$49-R$78.99, 重量5-6kg</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>79</v>
+      </c>
+      <c r="B69">
+        <v>99.99</v>
+      </c>
+      <c r="C69">
+        <v>5</v>
+      </c>
+      <c r="D69">
+        <v>6</v>
+      </c>
+      <c r="E69">
+        <v>25.45</v>
+      </c>
+      <c r="F69" t="str">
+        <v>售价R$79-R$99.99, 重量5-6kg</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>100</v>
+      </c>
+      <c r="B70">
+        <v>119.99</v>
+      </c>
+      <c r="C70">
+        <v>5</v>
+      </c>
+      <c r="D70">
+        <v>6</v>
+      </c>
+      <c r="E70">
+        <v>28.55</v>
+      </c>
+      <c r="F70" t="str">
+        <v>售价R$100-R$119.99, 重量5-6kg</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>120</v>
+      </c>
+      <c r="B71">
+        <v>149.99</v>
+      </c>
+      <c r="C71">
+        <v>5</v>
+      </c>
+      <c r="D71">
+        <v>6</v>
+      </c>
+      <c r="E71">
+        <v>32.65</v>
+      </c>
+      <c r="F71" t="str">
+        <v>售价R$120-R$149.99, 重量5-6kg</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>150</v>
+      </c>
+      <c r="B72">
+        <v>199.99</v>
+      </c>
+      <c r="C72">
+        <v>5</v>
+      </c>
+      <c r="D72">
+        <v>6</v>
+      </c>
+      <c r="E72">
+        <v>35.75</v>
+      </c>
+      <c r="F72" t="str">
+        <v>售价R$150-R$199.99, 重量5-6kg</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>200</v>
+      </c>
+      <c r="B73">
+        <v>99999</v>
+      </c>
+      <c r="C73">
+        <v>5</v>
+      </c>
+      <c r="D73">
+        <v>6</v>
+      </c>
+      <c r="E73">
+        <v>39.75</v>
+      </c>
+      <c r="F73" t="str">
+        <v>售价R$200-以上, 重量5-6kg</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0</v>
+      </c>
+      <c r="B74">
+        <v>18.99</v>
+      </c>
+      <c r="C74">
+        <v>6</v>
+      </c>
+      <c r="D74">
+        <v>7</v>
+      </c>
+      <c r="E74">
+        <v>6.75</v>
+      </c>
+      <c r="F74" t="str">
+        <v>售价R$0-R$18.99, 重量6-7kg</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>19</v>
+      </c>
+      <c r="B75">
+        <v>48.99</v>
+      </c>
+      <c r="C75">
+        <v>6</v>
+      </c>
+      <c r="D75">
+        <v>7</v>
+      </c>
+      <c r="E75">
+        <v>8.75</v>
+      </c>
+      <c r="F75" t="str">
+        <v>售价R$19-R$48.99, 重量6-7kg</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>49</v>
+      </c>
+      <c r="B76">
+        <v>78.99</v>
+      </c>
+      <c r="C76">
+        <v>6</v>
+      </c>
+      <c r="D76">
+        <v>7</v>
+      </c>
+      <c r="E76">
+        <v>10.15</v>
+      </c>
+      <c r="F76" t="str">
+        <v>售价R$49-R$78.99, 重量6-7kg</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>79</v>
+      </c>
+      <c r="B77">
+        <v>99.99</v>
+      </c>
+      <c r="C77">
+        <v>6</v>
+      </c>
+      <c r="D77">
+        <v>7</v>
+      </c>
+      <c r="E77">
+        <v>27.05</v>
+      </c>
+      <c r="F77" t="str">
+        <v>售价R$79-R$99.99, 重量6-7kg</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>100</v>
+      </c>
+      <c r="B78">
+        <v>119.99</v>
+      </c>
+      <c r="C78">
+        <v>6</v>
+      </c>
+      <c r="D78">
+        <v>7</v>
+      </c>
+      <c r="E78">
+        <v>31.05</v>
+      </c>
+      <c r="F78" t="str">
+        <v>售价R$100-R$119.99, 重量6-7kg</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>120</v>
+      </c>
+      <c r="B79">
+        <v>149.99</v>
+      </c>
+      <c r="C79">
+        <v>6</v>
+      </c>
+      <c r="D79">
+        <v>7</v>
+      </c>
+      <c r="E79">
+        <v>36.05</v>
+      </c>
+      <c r="F79" t="str">
+        <v>售价R$120-R$149.99, 重量6-7kg</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>150</v>
+      </c>
+      <c r="B80">
+        <v>199.99</v>
+      </c>
+      <c r="C80">
+        <v>6</v>
+      </c>
+      <c r="D80">
+        <v>7</v>
+      </c>
+      <c r="E80">
+        <v>40.05</v>
+      </c>
+      <c r="F80" t="str">
+        <v>售价R$150-R$199.99, 重量6-7kg</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>200</v>
+      </c>
+      <c r="B81">
+        <v>99999</v>
+      </c>
+      <c r="C81">
+        <v>6</v>
+      </c>
+      <c r="D81">
+        <v>7</v>
+      </c>
+      <c r="E81">
+        <v>44.05</v>
+      </c>
+      <c r="F81" t="str">
+        <v>售价R$200-以上, 重量6-7kg</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0</v>
+      </c>
+      <c r="B82">
+        <v>18.99</v>
+      </c>
+      <c r="C82">
+        <v>7</v>
+      </c>
+      <c r="D82">
+        <v>8</v>
+      </c>
+      <c r="E82">
+        <v>6.85</v>
+      </c>
+      <c r="F82" t="str">
+        <v>售价R$0-R$18.99, 重量7-8kg</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>19</v>
+      </c>
+      <c r="B83">
+        <v>48.99</v>
+      </c>
+      <c r="C83">
+        <v>7</v>
+      </c>
+      <c r="D83">
+        <v>8</v>
+      </c>
+      <c r="E83">
+        <v>8.95</v>
+      </c>
+      <c r="F83" t="str">
+        <v>售价R$19-R$48.99, 重量7-8kg</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>49</v>
+      </c>
+      <c r="B84">
+        <v>78.99</v>
+      </c>
+      <c r="C84">
+        <v>7</v>
+      </c>
+      <c r="D84">
+        <v>8</v>
+      </c>
+      <c r="E84">
+        <v>10.35</v>
+      </c>
+      <c r="F84" t="str">
+        <v>售价R$49-R$78.99, 重量7-8kg</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>79</v>
+      </c>
+      <c r="B85">
+        <v>99.99</v>
+      </c>
+      <c r="C85">
+        <v>7</v>
+      </c>
+      <c r="D85">
+        <v>8</v>
+      </c>
+      <c r="E85">
+        <v>28.85</v>
+      </c>
+      <c r="F85" t="str">
+        <v>售价R$79-R$99.99, 重量7-8kg</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>100</v>
+      </c>
+      <c r="B86">
+        <v>119.99</v>
+      </c>
+      <c r="C86">
+        <v>7</v>
+      </c>
+      <c r="D86">
+        <v>8</v>
+      </c>
+      <c r="E86">
+        <v>33.65</v>
+      </c>
+      <c r="F86" t="str">
+        <v>售价R$100-R$119.99, 重量7-8kg</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>120</v>
+      </c>
+      <c r="B87">
+        <v>149.99</v>
+      </c>
+      <c r="C87">
+        <v>7</v>
+      </c>
+      <c r="D87">
+        <v>8</v>
+      </c>
+      <c r="E87">
+        <v>38.45</v>
+      </c>
+      <c r="F87" t="str">
+        <v>售价R$120-R$149.99, 重量7-8kg</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>150</v>
+      </c>
+      <c r="B88">
+        <v>199.99</v>
+      </c>
+      <c r="C88">
+        <v>7</v>
+      </c>
+      <c r="D88">
+        <v>8</v>
+      </c>
+      <c r="E88">
+        <v>43.25</v>
+      </c>
+      <c r="F88" t="str">
+        <v>售价R$150-R$199.99, 重量7-8kg</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>200</v>
+      </c>
+      <c r="B89">
+        <v>99999</v>
+      </c>
+      <c r="C89">
+        <v>7</v>
+      </c>
+      <c r="D89">
+        <v>8</v>
+      </c>
+      <c r="E89">
+        <v>48.05</v>
+      </c>
+      <c r="F89" t="str">
+        <v>售价R$200-以上, 重量7-8kg</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0</v>
+      </c>
+      <c r="B90">
+        <v>18.99</v>
+      </c>
+      <c r="C90">
+        <v>8</v>
+      </c>
+      <c r="D90">
+        <v>9</v>
+      </c>
+      <c r="E90">
+        <v>6.95</v>
+      </c>
+      <c r="F90" t="str">
+        <v>售价R$0-R$18.99, 重量8-9kg</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>19</v>
+      </c>
+      <c r="B91">
+        <v>48.99</v>
+      </c>
+      <c r="C91">
+        <v>8</v>
+      </c>
+      <c r="D91">
+        <v>9</v>
+      </c>
+      <c r="E91">
+        <v>9.15</v>
+      </c>
+      <c r="F91" t="str">
+        <v>售价R$19-R$48.99, 重量8-9kg</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>49</v>
+      </c>
+      <c r="B92">
+        <v>78.99</v>
+      </c>
+      <c r="C92">
+        <v>8</v>
+      </c>
+      <c r="D92">
+        <v>9</v>
+      </c>
+      <c r="E92">
+        <v>10.55</v>
+      </c>
+      <c r="F92" t="str">
+        <v>售价R$49-R$78.99, 重量8-9kg</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>79</v>
+      </c>
+      <c r="B93">
+        <v>99.99</v>
+      </c>
+      <c r="C93">
+        <v>8</v>
+      </c>
+      <c r="D93">
+        <v>9</v>
+      </c>
+      <c r="E93">
+        <v>29.65</v>
+      </c>
+      <c r="F93" t="str">
+        <v>售价R$79-R$99.99, 重量8-9kg</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>100</v>
+      </c>
+      <c r="B94">
+        <v>119.99</v>
+      </c>
+      <c r="C94">
+        <v>8</v>
+      </c>
+      <c r="D94">
+        <v>9</v>
+      </c>
+      <c r="E94">
+        <v>34.55</v>
+      </c>
+      <c r="F94" t="str">
+        <v>售价R$100-R$119.99, 重量8-9kg</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>120</v>
+      </c>
+      <c r="B95">
+        <v>149.99</v>
+      </c>
+      <c r="C95">
+        <v>8</v>
+      </c>
+      <c r="D95">
+        <v>9</v>
+      </c>
+      <c r="E95">
+        <v>39.55</v>
+      </c>
+      <c r="F95" t="str">
+        <v>售价R$120-R$149.99, 重量8-9kg</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>150</v>
+      </c>
+      <c r="B96">
+        <v>199.99</v>
+      </c>
+      <c r="C96">
+        <v>8</v>
+      </c>
+      <c r="D96">
+        <v>9</v>
+      </c>
+      <c r="E96">
+        <v>44.45</v>
+      </c>
+      <c r="F96" t="str">
+        <v>售价R$150-R$199.99, 重量8-9kg</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>200</v>
+      </c>
+      <c r="B97">
+        <v>99999</v>
+      </c>
+      <c r="C97">
+        <v>8</v>
+      </c>
+      <c r="D97">
+        <v>9</v>
+      </c>
+      <c r="E97">
+        <v>49.35</v>
+      </c>
+      <c r="F97" t="str">
+        <v>售价R$200-以上, 重量8-9kg</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0</v>
+      </c>
+      <c r="B98">
+        <v>18.99</v>
+      </c>
+      <c r="C98">
+        <v>9</v>
+      </c>
+      <c r="D98">
+        <v>11</v>
+      </c>
+      <c r="E98">
+        <v>7.05</v>
+      </c>
+      <c r="F98" t="str">
+        <v>售价R$0-R$18.99, 重量9-11kg</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>19</v>
+      </c>
+      <c r="B99">
+        <v>48.99</v>
+      </c>
+      <c r="C99">
+        <v>9</v>
+      </c>
+      <c r="D99">
+        <v>11</v>
+      </c>
+      <c r="E99">
+        <v>9.55</v>
+      </c>
+      <c r="F99" t="str">
+        <v>售价R$19-R$48.99, 重量9-11kg</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>49</v>
+      </c>
+      <c r="B100">
+        <v>78.99</v>
+      </c>
+      <c r="C100">
+        <v>9</v>
+      </c>
+      <c r="D100">
+        <v>11</v>
+      </c>
+      <c r="E100">
+        <v>10.95</v>
+      </c>
+      <c r="F100" t="str">
+        <v>售价R$49-R$78.99, 重量9-11kg</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>79</v>
+      </c>
+      <c r="B101">
+        <v>99.99</v>
+      </c>
+      <c r="C101">
+        <v>9</v>
+      </c>
+      <c r="D101">
+        <v>11</v>
+      </c>
+      <c r="E101">
+        <v>41.25</v>
+      </c>
+      <c r="F101" t="str">
+        <v>售价R$79-R$99.99, 重量9-11kg</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="B102">
+        <v>119.99</v>
+      </c>
+      <c r="C102">
+        <v>9</v>
+      </c>
+      <c r="D102">
+        <v>11</v>
+      </c>
+      <c r="E102">
+        <v>48.05</v>
+      </c>
+      <c r="F102" t="str">
+        <v>售价R$100-R$119.99, 重量9-11kg</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>120</v>
+      </c>
+      <c r="B103">
+        <v>149.99</v>
+      </c>
+      <c r="C103">
+        <v>9</v>
+      </c>
+      <c r="D103">
+        <v>11</v>
+      </c>
+      <c r="E103">
+        <v>54.95</v>
+      </c>
+      <c r="F103" t="str">
+        <v>售价R$120-R$149.99, 重量9-11kg</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>150</v>
+      </c>
+      <c r="B104">
+        <v>199.99</v>
+      </c>
+      <c r="C104">
+        <v>9</v>
+      </c>
+      <c r="D104">
+        <v>11</v>
+      </c>
+      <c r="E104">
+        <v>61.75</v>
+      </c>
+      <c r="F104" t="str">
+        <v>售价R$150-R$199.99, 重量9-11kg</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>200</v>
+      </c>
+      <c r="B105">
+        <v>99999</v>
+      </c>
+      <c r="C105">
+        <v>9</v>
+      </c>
+      <c r="D105">
+        <v>11</v>
+      </c>
+      <c r="E105">
+        <v>68.65</v>
+      </c>
+      <c r="F105" t="str">
+        <v>售价R$200-以上, 重量9-11kg</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>0</v>
+      </c>
+      <c r="B106">
+        <v>18.99</v>
+      </c>
+      <c r="C106">
+        <v>11</v>
+      </c>
+      <c r="D106">
+        <v>13</v>
+      </c>
+      <c r="E106">
+        <v>7.15</v>
+      </c>
+      <c r="F106" t="str">
+        <v>售价R$0-R$18.99, 重量11-13kg</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>19</v>
+      </c>
+      <c r="B107">
+        <v>48.99</v>
+      </c>
+      <c r="C107">
+        <v>11</v>
+      </c>
+      <c r="D107">
+        <v>13</v>
+      </c>
+      <c r="E107">
+        <v>9.95</v>
+      </c>
+      <c r="F107" t="str">
+        <v>售价R$19-R$48.99, 重量11-13kg</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>49</v>
+      </c>
+      <c r="B108">
+        <v>78.99</v>
+      </c>
+      <c r="C108">
+        <v>11</v>
+      </c>
+      <c r="D108">
+        <v>13</v>
+      </c>
+      <c r="E108">
+        <v>11.35</v>
+      </c>
+      <c r="F108" t="str">
+        <v>售价R$49-R$78.99, 重量11-13kg</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>79</v>
+      </c>
+      <c r="B109">
+        <v>99.99</v>
+      </c>
+      <c r="C109">
+        <v>11</v>
+      </c>
+      <c r="D109">
+        <v>13</v>
+      </c>
+      <c r="E109">
+        <v>42.15</v>
+      </c>
+      <c r="F109" t="str">
+        <v>售价R$79-R$99.99, 重量11-13kg</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>100</v>
+      </c>
+      <c r="B110">
+        <v>119.99</v>
+      </c>
+      <c r="C110">
+        <v>11</v>
+      </c>
+      <c r="D110">
+        <v>13</v>
+      </c>
+      <c r="E110">
+        <v>49.25</v>
+      </c>
+      <c r="F110" t="str">
+        <v>售价R$100-R$119.99, 重量11-13kg</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>120</v>
+      </c>
+      <c r="B111">
+        <v>149.99</v>
+      </c>
+      <c r="C111">
+        <v>11</v>
+      </c>
+      <c r="D111">
+        <v>13</v>
+      </c>
+      <c r="E111">
+        <v>56.25</v>
+      </c>
+      <c r="F111" t="str">
+        <v>售价R$120-R$149.99, 重量11-13kg</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>150</v>
+      </c>
+      <c r="B112">
+        <v>199.99</v>
+      </c>
+      <c r="C112">
+        <v>11</v>
+      </c>
+      <c r="D112">
+        <v>13</v>
+      </c>
+      <c r="E112">
+        <v>63.25</v>
+      </c>
+      <c r="F112" t="str">
+        <v>售价R$150-R$199.99, 重量11-13kg</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>200</v>
+      </c>
+      <c r="B113">
+        <v>99999</v>
+      </c>
+      <c r="C113">
+        <v>11</v>
+      </c>
+      <c r="D113">
+        <v>13</v>
+      </c>
+      <c r="E113">
+        <v>70.25</v>
+      </c>
+      <c r="F113" t="str">
+        <v>售价R$200-以上, 重量11-13kg</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>0</v>
+      </c>
+      <c r="B114">
+        <v>18.99</v>
+      </c>
+      <c r="C114">
+        <v>13</v>
+      </c>
+      <c r="D114">
+        <v>15</v>
+      </c>
+      <c r="E114">
+        <v>7.25</v>
+      </c>
+      <c r="F114" t="str">
+        <v>售价R$0-R$18.99, 重量13-15kg</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>19</v>
+      </c>
+      <c r="B115">
+        <v>48.99</v>
+      </c>
+      <c r="C115">
+        <v>13</v>
+      </c>
+      <c r="D115">
+        <v>15</v>
+      </c>
+      <c r="E115">
+        <v>10.15</v>
+      </c>
+      <c r="F115" t="str">
+        <v>售价R$19-R$48.99, 重量13-15kg</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>49</v>
+      </c>
+      <c r="B116">
+        <v>78.99</v>
+      </c>
+      <c r="C116">
+        <v>13</v>
+      </c>
+      <c r="D116">
+        <v>15</v>
+      </c>
+      <c r="E116">
+        <v>11.55</v>
+      </c>
+      <c r="F116" t="str">
+        <v>售价R$49-R$78.99, 重量13-15kg</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>79</v>
+      </c>
+      <c r="B117">
+        <v>99.99</v>
+      </c>
+      <c r="C117">
+        <v>13</v>
+      </c>
+      <c r="D117">
+        <v>15</v>
+      </c>
+      <c r="E117">
+        <v>45.05</v>
+      </c>
+      <c r="F117" t="str">
+        <v>售价R$79-R$99.99, 重量13-15kg</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>100</v>
+      </c>
+      <c r="B118">
+        <v>119.99</v>
+      </c>
+      <c r="C118">
+        <v>13</v>
+      </c>
+      <c r="D118">
+        <v>15</v>
+      </c>
+      <c r="E118">
+        <v>52.45</v>
+      </c>
+      <c r="F118" t="str">
+        <v>售价R$100-R$119.99, 重量13-15kg</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>120</v>
+      </c>
+      <c r="B119">
+        <v>149.99</v>
+      </c>
+      <c r="C119">
+        <v>13</v>
+      </c>
+      <c r="D119">
+        <v>15</v>
+      </c>
+      <c r="E119">
+        <v>59.95</v>
+      </c>
+      <c r="F119" t="str">
+        <v>售价R$120-R$149.99, 重量13-15kg</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>150</v>
+      </c>
+      <c r="B120">
+        <v>199.99</v>
+      </c>
+      <c r="C120">
+        <v>13</v>
+      </c>
+      <c r="D120">
+        <v>15</v>
+      </c>
+      <c r="E120">
+        <v>67.45</v>
+      </c>
+      <c r="F120" t="str">
+        <v>售价R$150-R$199.99, 重量13-15kg</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>200</v>
+      </c>
+      <c r="B121">
+        <v>99999</v>
+      </c>
+      <c r="C121">
+        <v>13</v>
+      </c>
+      <c r="D121">
+        <v>15</v>
+      </c>
+      <c r="E121">
+        <v>74.95</v>
+      </c>
+      <c r="F121" t="str">
+        <v>售价R$200-以上, 重量13-15kg</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>0</v>
+      </c>
+      <c r="B122">
+        <v>18.99</v>
+      </c>
+      <c r="C122">
+        <v>15</v>
+      </c>
+      <c r="D122">
+        <v>17</v>
+      </c>
+      <c r="E122">
+        <v>7.35</v>
+      </c>
+      <c r="F122" t="str">
+        <v>售价R$0-R$18.99, 重量15-17kg</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>19</v>
+      </c>
+      <c r="B123">
+        <v>48.99</v>
+      </c>
+      <c r="C123">
+        <v>15</v>
+      </c>
+      <c r="D123">
+        <v>17</v>
+      </c>
+      <c r="E123">
+        <v>10.35</v>
+      </c>
+      <c r="F123" t="str">
+        <v>售价R$19-R$48.99, 重量15-17kg</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>49</v>
+      </c>
+      <c r="B124">
+        <v>78.99</v>
+      </c>
+      <c r="C124">
+        <v>15</v>
+      </c>
+      <c r="D124">
+        <v>17</v>
+      </c>
+      <c r="E124">
+        <v>11.75</v>
+      </c>
+      <c r="F124" t="str">
+        <v>售价R$49-R$78.99, 重量15-17kg</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>79</v>
+      </c>
+      <c r="B125">
+        <v>99.99</v>
+      </c>
+      <c r="C125">
+        <v>15</v>
+      </c>
+      <c r="D125">
+        <v>17</v>
+      </c>
+      <c r="E125">
+        <v>48.55</v>
+      </c>
+      <c r="F125" t="str">
+        <v>售价R$79-R$99.99, 重量15-17kg</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>100</v>
+      </c>
+      <c r="B126">
+        <v>119.99</v>
+      </c>
+      <c r="C126">
+        <v>15</v>
+      </c>
+      <c r="D126">
+        <v>17</v>
+      </c>
+      <c r="E126">
+        <v>56.05</v>
+      </c>
+      <c r="F126" t="str">
+        <v>售价R$100-R$119.99, 重量15-17kg</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>120</v>
+      </c>
+      <c r="B127">
+        <v>149.99</v>
+      </c>
+      <c r="C127">
+        <v>15</v>
+      </c>
+      <c r="D127">
+        <v>17</v>
+      </c>
+      <c r="E127">
+        <v>63.55</v>
+      </c>
+      <c r="F127" t="str">
+        <v>售价R$120-R$149.99, 重量15-17kg</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>150</v>
+      </c>
+      <c r="B128">
+        <v>199.99</v>
+      </c>
+      <c r="C128">
+        <v>15</v>
+      </c>
+      <c r="D128">
+        <v>17</v>
+      </c>
+      <c r="E128">
+        <v>70.75</v>
+      </c>
+      <c r="F128" t="str">
+        <v>售价R$150-R$199.99, 重量15-17kg</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>200</v>
+      </c>
+      <c r="B129">
+        <v>99999</v>
+      </c>
+      <c r="C129">
+        <v>15</v>
+      </c>
+      <c r="D129">
+        <v>17</v>
+      </c>
+      <c r="E129">
+        <v>78.65</v>
+      </c>
+      <c r="F129" t="str">
+        <v>售价R$200-以上, 重量15-17kg</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>0</v>
+      </c>
+      <c r="B130">
+        <v>18.99</v>
+      </c>
+      <c r="C130">
+        <v>17</v>
+      </c>
+      <c r="D130">
+        <v>20</v>
+      </c>
+      <c r="E130">
+        <v>7.45</v>
+      </c>
+      <c r="F130" t="str">
+        <v>售价R$0-R$18.99, 重量17-20kg</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>19</v>
+      </c>
+      <c r="B131">
+        <v>48.99</v>
+      </c>
+      <c r="C131">
+        <v>17</v>
+      </c>
+      <c r="D131">
+        <v>20</v>
+      </c>
+      <c r="E131">
+        <v>10.55</v>
+      </c>
+      <c r="F131" t="str">
+        <v>售价R$19-R$48.99, 重量17-20kg</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>49</v>
+      </c>
+      <c r="B132">
+        <v>78.99</v>
+      </c>
+      <c r="C132">
+        <v>17</v>
+      </c>
+      <c r="D132">
+        <v>20</v>
+      </c>
+      <c r="E132">
+        <v>11.95</v>
+      </c>
+      <c r="F132" t="str">
+        <v>售价R$49-R$78.99, 重量17-20kg</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>79</v>
+      </c>
+      <c r="B133">
+        <v>99.99</v>
+      </c>
+      <c r="C133">
+        <v>17</v>
+      </c>
+      <c r="D133">
+        <v>20</v>
+      </c>
+      <c r="E133">
+        <v>54.75</v>
+      </c>
+      <c r="F133" t="str">
+        <v>售价R$79-R$99.99, 重量17-20kg</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>100</v>
+      </c>
+      <c r="B134">
+        <v>119.99</v>
+      </c>
+      <c r="C134">
+        <v>17</v>
+      </c>
+      <c r="D134">
+        <v>20</v>
+      </c>
+      <c r="E134">
+        <v>63.85</v>
+      </c>
+      <c r="F134" t="str">
+        <v>售价R$100-R$119.99, 重量17-20kg</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>120</v>
+      </c>
+      <c r="B135">
+        <v>149.99</v>
+      </c>
+      <c r="C135">
+        <v>17</v>
+      </c>
+      <c r="D135">
+        <v>20</v>
+      </c>
+      <c r="E135">
+        <v>72.95</v>
+      </c>
+      <c r="F135" t="str">
+        <v>售价R$120-R$149.99, 重量17-20kg</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>150</v>
+      </c>
+      <c r="B136">
+        <v>199.99</v>
+      </c>
+      <c r="C136">
+        <v>17</v>
+      </c>
+      <c r="D136">
+        <v>20</v>
+      </c>
+      <c r="E136">
+        <v>82.05</v>
+      </c>
+      <c r="F136" t="str">
+        <v>售价R$150-R$199.99, 重量17-20kg</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>200</v>
+      </c>
+      <c r="B137">
+        <v>99999</v>
+      </c>
+      <c r="C137">
+        <v>17</v>
+      </c>
+      <c r="D137">
+        <v>20</v>
+      </c>
+      <c r="E137">
+        <v>91.15</v>
+      </c>
+      <c r="F137" t="str">
+        <v>售价R$200-以上, 重量17-20kg</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>0</v>
+      </c>
+      <c r="B138">
+        <v>18.99</v>
+      </c>
+      <c r="C138">
+        <v>20</v>
+      </c>
+      <c r="D138">
+        <v>25</v>
+      </c>
+      <c r="E138">
+        <v>7.65</v>
+      </c>
+      <c r="F138" t="str">
+        <v>售价R$0-R$18.99, 重量20-25kg</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>19</v>
+      </c>
+      <c r="B139">
+        <v>48.99</v>
+      </c>
+      <c r="C139">
+        <v>20</v>
+      </c>
+      <c r="D139">
+        <v>25</v>
+      </c>
+      <c r="E139">
+        <v>10.95</v>
+      </c>
+      <c r="F139" t="str">
+        <v>售价R$19-R$48.99, 重量20-25kg</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>49</v>
+      </c>
+      <c r="B140">
+        <v>78.99</v>
+      </c>
+      <c r="C140">
+        <v>20</v>
+      </c>
+      <c r="D140">
+        <v>25</v>
+      </c>
+      <c r="E140">
+        <v>12.15</v>
+      </c>
+      <c r="F140" t="str">
+        <v>售价R$49-R$78.99, 重量20-25kg</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>79</v>
+      </c>
+      <c r="B141">
+        <v>99.99</v>
+      </c>
+      <c r="C141">
+        <v>20</v>
+      </c>
+      <c r="D141">
+        <v>25</v>
+      </c>
+      <c r="E141">
+        <v>64.05</v>
+      </c>
+      <c r="F141" t="str">
+        <v>售价R$79-R$99.99, 重量20-25kg</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>100</v>
+      </c>
+      <c r="B142">
+        <v>119.99</v>
+      </c>
+      <c r="C142">
+        <v>20</v>
+      </c>
+      <c r="D142">
+        <v>25</v>
+      </c>
+      <c r="E142">
+        <v>75.05</v>
+      </c>
+      <c r="F142" t="str">
+        <v>售价R$100-R$119.99, 重量20-25kg</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>120</v>
+      </c>
+      <c r="B143">
+        <v>149.99</v>
+      </c>
+      <c r="C143">
+        <v>20</v>
+      </c>
+      <c r="D143">
+        <v>25</v>
+      </c>
+      <c r="E143">
+        <v>84.75</v>
+      </c>
+      <c r="F143" t="str">
+        <v>售价R$120-R$149.99, 重量20-25kg</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>150</v>
+      </c>
+      <c r="B144">
+        <v>199.99</v>
+      </c>
+      <c r="C144">
+        <v>20</v>
+      </c>
+      <c r="D144">
+        <v>25</v>
+      </c>
+      <c r="E144">
+        <v>95.35</v>
+      </c>
+      <c r="F144" t="str">
+        <v>售价R$150-R$199.99, 重量20-25kg</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>200</v>
+      </c>
+      <c r="B145">
+        <v>99999</v>
+      </c>
+      <c r="C145">
+        <v>20</v>
+      </c>
+      <c r="D145">
+        <v>25</v>
+      </c>
+      <c r="E145">
+        <v>105.95</v>
+      </c>
+      <c r="F145" t="str">
+        <v>售价R$200-以上, 重量20-25kg</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>0</v>
+      </c>
+      <c r="B146">
+        <v>18.99</v>
+      </c>
+      <c r="C146">
+        <v>25</v>
+      </c>
+      <c r="D146">
+        <v>30</v>
+      </c>
+      <c r="E146">
+        <v>7.75</v>
+      </c>
+      <c r="F146" t="str">
+        <v>售价R$0-R$18.99, 重量25-30kg</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>19</v>
+      </c>
+      <c r="B147">
+        <v>48.99</v>
+      </c>
+      <c r="C147">
+        <v>25</v>
+      </c>
+      <c r="D147">
+        <v>30</v>
+      </c>
+      <c r="E147">
+        <v>11.15</v>
+      </c>
+      <c r="F147" t="str">
+        <v>售价R$19-R$48.99, 重量25-30kg</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>49</v>
+      </c>
+      <c r="B148">
+        <v>78.99</v>
+      </c>
+      <c r="C148">
+        <v>25</v>
+      </c>
+      <c r="D148">
+        <v>30</v>
+      </c>
+      <c r="E148">
+        <v>12.35</v>
+      </c>
+      <c r="F148" t="str">
+        <v>售价R$49-R$78.99, 重量25-30kg</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>79</v>
+      </c>
+      <c r="B149">
+        <v>99.99</v>
+      </c>
+      <c r="C149">
+        <v>25</v>
+      </c>
+      <c r="D149">
+        <v>30</v>
+      </c>
+      <c r="E149">
+        <v>65.95</v>
+      </c>
+      <c r="F149" t="str">
+        <v>售价R$79-R$99.99, 重量25-30kg</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>100</v>
+      </c>
+      <c r="B150">
+        <v>119.99</v>
+      </c>
+      <c r="C150">
+        <v>25</v>
+      </c>
+      <c r="D150">
+        <v>30</v>
+      </c>
+      <c r="E150">
+        <v>75.45</v>
+      </c>
+      <c r="F150" t="str">
+        <v>售价R$100-R$119.99, 重量25-30kg</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>120</v>
+      </c>
+      <c r="B151">
+        <v>149.99</v>
+      </c>
+      <c r="C151">
+        <v>25</v>
+      </c>
+      <c r="D151">
+        <v>30</v>
+      </c>
+      <c r="E151">
+        <v>85.55</v>
+      </c>
+      <c r="F151" t="str">
+        <v>售价R$120-R$149.99, 重量25-30kg</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>150</v>
+      </c>
+      <c r="B152">
+        <v>199.99</v>
+      </c>
+      <c r="C152">
+        <v>25</v>
+      </c>
+      <c r="D152">
+        <v>30</v>
+      </c>
+      <c r="E152">
+        <v>96.25</v>
+      </c>
+      <c r="F152" t="str">
+        <v>售价R$150-R$199.99, 重量25-30kg</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>200</v>
+      </c>
+      <c r="B153">
+        <v>99999</v>
+      </c>
+      <c r="C153">
+        <v>25</v>
+      </c>
+      <c r="D153">
+        <v>30</v>
+      </c>
+      <c r="E153">
+        <v>106.95</v>
+      </c>
+      <c r="F153" t="str">
+        <v>售价R$200-以上, 重量25-30kg</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>0</v>
+      </c>
+      <c r="B154">
+        <v>18.99</v>
+      </c>
+      <c r="C154">
+        <v>30</v>
+      </c>
+      <c r="D154">
+        <v>40</v>
+      </c>
+      <c r="E154">
+        <v>7.85</v>
+      </c>
+      <c r="F154" t="str">
+        <v>售价R$0-R$18.99, 重量30-40kg</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>19</v>
+      </c>
+      <c r="B155">
+        <v>48.99</v>
+      </c>
+      <c r="C155">
+        <v>30</v>
+      </c>
+      <c r="D155">
+        <v>40</v>
+      </c>
+      <c r="E155">
+        <v>11.35</v>
+      </c>
+      <c r="F155" t="str">
+        <v>售价R$19-R$48.99, 重量30-40kg</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>49</v>
+      </c>
+      <c r="B156">
+        <v>78.99</v>
+      </c>
+      <c r="C156">
+        <v>30</v>
+      </c>
+      <c r="D156">
+        <v>40</v>
+      </c>
+      <c r="E156">
+        <v>12.55</v>
+      </c>
+      <c r="F156" t="str">
+        <v>售价R$49-R$78.99, 重量30-40kg</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>79</v>
+      </c>
+      <c r="B157">
+        <v>99.99</v>
+      </c>
+      <c r="C157">
+        <v>30</v>
+      </c>
+      <c r="D157">
+        <v>40</v>
+      </c>
+      <c r="E157">
+        <v>67.75</v>
+      </c>
+      <c r="F157" t="str">
+        <v>售价R$79-R$99.99, 重量30-40kg</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>100</v>
+      </c>
+      <c r="B158">
+        <v>119.99</v>
+      </c>
+      <c r="C158">
+        <v>30</v>
+      </c>
+      <c r="D158">
+        <v>40</v>
+      </c>
+      <c r="E158">
+        <v>78.95</v>
+      </c>
+      <c r="F158" t="str">
+        <v>售价R$100-R$119.99, 重量30-40kg</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>120</v>
+      </c>
+      <c r="B159">
+        <v>149.99</v>
+      </c>
+      <c r="C159">
+        <v>30</v>
+      </c>
+      <c r="D159">
+        <v>40</v>
+      </c>
+      <c r="E159">
+        <v>88.95</v>
+      </c>
+      <c r="F159" t="str">
+        <v>售价R$120-R$149.99, 重量30-40kg</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>150</v>
+      </c>
+      <c r="B160">
+        <v>199.99</v>
+      </c>
+      <c r="C160">
+        <v>30</v>
+      </c>
+      <c r="D160">
+        <v>40</v>
+      </c>
+      <c r="E160">
+        <v>99.15</v>
+      </c>
+      <c r="F160" t="str">
+        <v>售价R$150-R$199.99, 重量30-40kg</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>200</v>
+      </c>
+      <c r="B161">
+        <v>99999</v>
+      </c>
+      <c r="C161">
+        <v>30</v>
+      </c>
+      <c r="D161">
+        <v>40</v>
+      </c>
+      <c r="E161">
+        <v>107.05</v>
+      </c>
+      <c r="F161" t="str">
+        <v>售价R$200-以上, 重量30-40kg</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>0</v>
+      </c>
+      <c r="B162">
+        <v>18.99</v>
+      </c>
+      <c r="C162">
+        <v>40</v>
+      </c>
+      <c r="D162">
+        <v>50</v>
+      </c>
+      <c r="E162">
+        <v>7.95</v>
+      </c>
+      <c r="F162" t="str">
+        <v>售价R$0-R$18.99, 重量40-50kg</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>19</v>
+      </c>
+      <c r="B163">
+        <v>48.99</v>
+      </c>
+      <c r="C163">
+        <v>40</v>
+      </c>
+      <c r="D163">
+        <v>50</v>
+      </c>
+      <c r="E163">
+        <v>11.55</v>
+      </c>
+      <c r="F163" t="str">
+        <v>售价R$19-R$48.99, 重量40-50kg</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>49</v>
+      </c>
+      <c r="B164">
+        <v>78.99</v>
+      </c>
+      <c r="C164">
+        <v>40</v>
+      </c>
+      <c r="D164">
+        <v>50</v>
+      </c>
+      <c r="E164">
+        <v>12.75</v>
+      </c>
+      <c r="F164" t="str">
+        <v>售价R$49-R$78.99, 重量40-50kg</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>79</v>
+      </c>
+      <c r="B165">
+        <v>99.99</v>
+      </c>
+      <c r="C165">
+        <v>40</v>
+      </c>
+      <c r="D165">
+        <v>50</v>
+      </c>
+      <c r="E165">
+        <v>70.25</v>
+      </c>
+      <c r="F165" t="str">
+        <v>售价R$79-R$99.99, 重量40-50kg</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>100</v>
+      </c>
+      <c r="B166">
+        <v>119.99</v>
+      </c>
+      <c r="C166">
+        <v>40</v>
+      </c>
+      <c r="D166">
+        <v>50</v>
+      </c>
+      <c r="E166">
+        <v>81.05</v>
+      </c>
+      <c r="F166" t="str">
+        <v>售价R$100-R$119.99, 重量40-50kg</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>120</v>
+      </c>
+      <c r="B167">
+        <v>149.99</v>
+      </c>
+      <c r="C167">
+        <v>40</v>
+      </c>
+      <c r="D167">
+        <v>50</v>
+      </c>
+      <c r="E167">
+        <v>92.05</v>
+      </c>
+      <c r="F167" t="str">
+        <v>售价R$120-R$149.99, 重量40-50kg</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>150</v>
+      </c>
+      <c r="B168">
+        <v>199.99</v>
+      </c>
+      <c r="C168">
+        <v>40</v>
+      </c>
+      <c r="D168">
+        <v>50</v>
+      </c>
+      <c r="E168">
+        <v>102.55</v>
+      </c>
+      <c r="F168" t="str">
+        <v>售价R$150-R$199.99, 重量40-50kg</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>200</v>
+      </c>
+      <c r="B169">
+        <v>99999</v>
+      </c>
+      <c r="C169">
+        <v>40</v>
+      </c>
+      <c r="D169">
+        <v>50</v>
+      </c>
+      <c r="E169">
+        <v>110.75</v>
+      </c>
+      <c r="F169" t="str">
+        <v>售价R$200-以上, 重量40-50kg</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>0</v>
+      </c>
+      <c r="B170">
+        <v>18.99</v>
+      </c>
+      <c r="C170">
+        <v>50</v>
+      </c>
+      <c r="D170">
+        <v>60</v>
+      </c>
+      <c r="E170">
+        <v>8.05</v>
+      </c>
+      <c r="F170" t="str">
+        <v>售价R$0-R$18.99, 重量50-60kg</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>19</v>
+      </c>
+      <c r="B171">
+        <v>48.99</v>
+      </c>
+      <c r="C171">
+        <v>50</v>
+      </c>
+      <c r="D171">
+        <v>60</v>
+      </c>
+      <c r="E171">
+        <v>11.75</v>
+      </c>
+      <c r="F171" t="str">
+        <v>售价R$19-R$48.99, 重量50-60kg</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>49</v>
+      </c>
+      <c r="B172">
+        <v>78.99</v>
+      </c>
+      <c r="C172">
+        <v>50</v>
+      </c>
+      <c r="D172">
+        <v>60</v>
+      </c>
+      <c r="E172">
+        <v>12.95</v>
+      </c>
+      <c r="F172" t="str">
+        <v>售价R$49-R$78.99, 重量50-60kg</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>79</v>
+      </c>
+      <c r="B173">
+        <v>99.99</v>
+      </c>
+      <c r="C173">
+        <v>50</v>
+      </c>
+      <c r="D173">
+        <v>60</v>
+      </c>
+      <c r="E173">
+        <v>74.95</v>
+      </c>
+      <c r="F173" t="str">
+        <v>售价R$79-R$99.99, 重量50-60kg</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>100</v>
+      </c>
+      <c r="B174">
+        <v>119.99</v>
+      </c>
+      <c r="C174">
+        <v>50</v>
+      </c>
+      <c r="D174">
+        <v>60</v>
+      </c>
+      <c r="E174">
+        <v>86.45</v>
+      </c>
+      <c r="F174" t="str">
+        <v>售价R$100-R$119.99, 重量50-60kg</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>120</v>
+      </c>
+      <c r="B175">
+        <v>149.99</v>
+      </c>
+      <c r="C175">
+        <v>50</v>
+      </c>
+      <c r="D175">
+        <v>60</v>
+      </c>
+      <c r="E175">
+        <v>98.15</v>
+      </c>
+      <c r="F175" t="str">
+        <v>售价R$120-R$149.99, 重量50-60kg</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>150</v>
+      </c>
+      <c r="B176">
+        <v>199.99</v>
+      </c>
+      <c r="C176">
+        <v>50</v>
+      </c>
+      <c r="D176">
+        <v>60</v>
+      </c>
+      <c r="E176">
+        <v>109.35</v>
+      </c>
+      <c r="F176" t="str">
+        <v>售价R$150-R$199.99, 重量50-60kg</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>200</v>
+      </c>
+      <c r="B177">
+        <v>99999</v>
+      </c>
+      <c r="C177">
+        <v>50</v>
+      </c>
+      <c r="D177">
+        <v>60</v>
+      </c>
+      <c r="E177">
+        <v>118.15</v>
+      </c>
+      <c r="F177" t="str">
+        <v>售价R$200-以上, 重量50-60kg</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>0</v>
+      </c>
+      <c r="B178">
+        <v>18.99</v>
+      </c>
+      <c r="C178">
+        <v>60</v>
+      </c>
+      <c r="D178">
+        <v>70</v>
+      </c>
+      <c r="E178">
+        <v>8.15</v>
+      </c>
+      <c r="F178" t="str">
+        <v>售价R$0-R$18.99, 重量60-70kg</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>19</v>
+      </c>
+      <c r="B179">
+        <v>48.99</v>
+      </c>
+      <c r="C179">
+        <v>60</v>
+      </c>
+      <c r="D179">
+        <v>70</v>
+      </c>
+      <c r="E179">
+        <v>11.95</v>
+      </c>
+      <c r="F179" t="str">
+        <v>售价R$19-R$48.99, 重量60-70kg</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>49</v>
+      </c>
+      <c r="B180">
+        <v>78.99</v>
+      </c>
+      <c r="C180">
+        <v>60</v>
+      </c>
+      <c r="D180">
+        <v>70</v>
+      </c>
+      <c r="E180">
+        <v>13.15</v>
+      </c>
+      <c r="F180" t="str">
+        <v>售价R$49-R$78.99, 重量60-70kg</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>79</v>
+      </c>
+      <c r="B181">
+        <v>99.99</v>
+      </c>
+      <c r="C181">
+        <v>60</v>
+      </c>
+      <c r="D181">
+        <v>70</v>
+      </c>
+      <c r="E181">
+        <v>80.25</v>
+      </c>
+      <c r="F181" t="str">
+        <v>售价R$79-R$99.99, 重量60-70kg</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>100</v>
+      </c>
+      <c r="B182">
+        <v>119.99</v>
+      </c>
+      <c r="C182">
+        <v>60</v>
+      </c>
+      <c r="D182">
+        <v>70</v>
+      </c>
+      <c r="E182">
+        <v>92.95</v>
+      </c>
+      <c r="F182" t="str">
+        <v>售价R$100-R$119.99, 重量60-70kg</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>120</v>
+      </c>
+      <c r="B183">
+        <v>149.99</v>
+      </c>
+      <c r="C183">
+        <v>60</v>
+      </c>
+      <c r="D183">
+        <v>70</v>
+      </c>
+      <c r="E183">
+        <v>105.05</v>
+      </c>
+      <c r="F183" t="str">
+        <v>售价R$120-R$149.99, 重量60-70kg</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>150</v>
+      </c>
+      <c r="B184">
+        <v>199.99</v>
+      </c>
+      <c r="C184">
+        <v>60</v>
+      </c>
+      <c r="D184">
+        <v>70</v>
+      </c>
+      <c r="E184">
+        <v>117.15</v>
+      </c>
+      <c r="F184" t="str">
+        <v>售价R$150-R$199.99, 重量60-70kg</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>200</v>
+      </c>
+      <c r="B185">
+        <v>99999</v>
+      </c>
+      <c r="C185">
+        <v>60</v>
+      </c>
+      <c r="D185">
+        <v>70</v>
+      </c>
+      <c r="E185">
+        <v>126.55</v>
+      </c>
+      <c r="F185" t="str">
+        <v>售价R$200-以上, 重量60-70kg</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>0</v>
+      </c>
+      <c r="B186">
+        <v>18.99</v>
+      </c>
+      <c r="C186">
+        <v>70</v>
+      </c>
+      <c r="D186">
+        <v>80</v>
+      </c>
+      <c r="E186">
+        <v>8.25</v>
+      </c>
+      <c r="F186" t="str">
+        <v>售价R$0-R$18.99, 重量70-80kg</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>19</v>
+      </c>
+      <c r="B187">
+        <v>48.99</v>
+      </c>
+      <c r="C187">
+        <v>70</v>
+      </c>
+      <c r="D187">
+        <v>80</v>
+      </c>
+      <c r="E187">
+        <v>12.15</v>
+      </c>
+      <c r="F187" t="str">
+        <v>售价R$19-R$48.99, 重量70-80kg</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>49</v>
+      </c>
+      <c r="B188">
+        <v>78.99</v>
+      </c>
+      <c r="C188">
+        <v>70</v>
+      </c>
+      <c r="D188">
+        <v>80</v>
+      </c>
+      <c r="E188">
+        <v>13.35</v>
+      </c>
+      <c r="F188" t="str">
+        <v>售价R$49-R$78.99, 重量70-80kg</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>79</v>
+      </c>
+      <c r="B189">
+        <v>99.99</v>
+      </c>
+      <c r="C189">
+        <v>70</v>
+      </c>
+      <c r="D189">
+        <v>80</v>
+      </c>
+      <c r="E189">
+        <v>83.95</v>
+      </c>
+      <c r="F189" t="str">
+        <v>售价R$79-R$99.99, 重量70-80kg</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>100</v>
+      </c>
+      <c r="B190">
+        <v>119.99</v>
+      </c>
+      <c r="C190">
+        <v>70</v>
+      </c>
+      <c r="D190">
+        <v>80</v>
+      </c>
+      <c r="E190">
+        <v>97.05</v>
+      </c>
+      <c r="F190" t="str">
+        <v>售价R$100-R$119.99, 重量70-80kg</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>120</v>
+      </c>
+      <c r="B191">
+        <v>149.99</v>
+      </c>
+      <c r="C191">
+        <v>70</v>
+      </c>
+      <c r="D191">
+        <v>80</v>
+      </c>
+      <c r="E191">
+        <v>109.85</v>
+      </c>
+      <c r="F191" t="str">
+        <v>售价R$120-R$149.99, 重量70-80kg</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>150</v>
+      </c>
+      <c r="B192">
+        <v>199.99</v>
+      </c>
+      <c r="C192">
+        <v>70</v>
+      </c>
+      <c r="D192">
+        <v>80</v>
+      </c>
+      <c r="E192">
+        <v>122.45</v>
+      </c>
+      <c r="F192" t="str">
+        <v>售价R$150-R$199.99, 重量70-80kg</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>200</v>
+      </c>
+      <c r="B193">
+        <v>99999</v>
+      </c>
+      <c r="C193">
+        <v>70</v>
+      </c>
+      <c r="D193">
+        <v>80</v>
+      </c>
+      <c r="E193">
+        <v>132.25</v>
+      </c>
+      <c r="F193" t="str">
+        <v>售价R$200-以上, 重量70-80kg</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>0</v>
+      </c>
+      <c r="B194">
+        <v>18.99</v>
+      </c>
+      <c r="C194">
+        <v>80</v>
+      </c>
+      <c r="D194">
+        <v>90</v>
+      </c>
+      <c r="E194">
+        <v>8.35</v>
+      </c>
+      <c r="F194" t="str">
+        <v>售价R$0-R$18.99, 重量80-90kg</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>19</v>
+      </c>
+      <c r="B195">
+        <v>48.99</v>
+      </c>
+      <c r="C195">
+        <v>80</v>
+      </c>
+      <c r="D195">
+        <v>90</v>
+      </c>
+      <c r="E195">
+        <v>12.35</v>
+      </c>
+      <c r="F195" t="str">
+        <v>售价R$19-R$48.99, 重量80-90kg</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>49</v>
+      </c>
+      <c r="B196">
+        <v>78.99</v>
+      </c>
+      <c r="C196">
+        <v>80</v>
+      </c>
+      <c r="D196">
+        <v>90</v>
+      </c>
+      <c r="E196">
+        <v>13.55</v>
+      </c>
+      <c r="F196" t="str">
+        <v>售价R$49-R$78.99, 重量80-90kg</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>79</v>
+      </c>
+      <c r="B197">
+        <v>99.99</v>
+      </c>
+      <c r="C197">
+        <v>80</v>
+      </c>
+      <c r="D197">
+        <v>90</v>
+      </c>
+      <c r="E197">
+        <v>93.25</v>
+      </c>
+      <c r="F197" t="str">
+        <v>售价R$79-R$99.99, 重量80-90kg</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>100</v>
+      </c>
+      <c r="B198">
+        <v>119.99</v>
+      </c>
+      <c r="C198">
+        <v>80</v>
+      </c>
+      <c r="D198">
+        <v>90</v>
+      </c>
+      <c r="E198">
+        <v>107.45</v>
+      </c>
+      <c r="F198" t="str">
+        <v>售价R$100-R$119.99, 重量80-90kg</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>120</v>
+      </c>
+      <c r="B199">
+        <v>149.99</v>
+      </c>
+      <c r="C199">
+        <v>80</v>
+      </c>
+      <c r="D199">
+        <v>90</v>
+      </c>
+      <c r="E199">
+        <v>122.05</v>
+      </c>
+      <c r="F199" t="str">
+        <v>售价R$120-R$149.99, 重量80-90kg</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>150</v>
+      </c>
+      <c r="B200">
+        <v>199.99</v>
+      </c>
+      <c r="C200">
+        <v>80</v>
+      </c>
+      <c r="D200">
+        <v>90</v>
+      </c>
+      <c r="E200">
+        <v>136.05</v>
+      </c>
+      <c r="F200" t="str">
+        <v>售价R$150-R$199.99, 重量80-90kg</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>99999</v>
+      </c>
+      <c r="C201">
+        <v>80</v>
+      </c>
+      <c r="D201">
+        <v>90</v>
+      </c>
+      <c r="E201">
+        <v>146.95</v>
+      </c>
+      <c r="F201" t="str">
+        <v>售价R$200-以上, 重量80-90kg</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>0</v>
+      </c>
+      <c r="B202">
+        <v>18.99</v>
+      </c>
+      <c r="C202">
+        <v>90</v>
+      </c>
+      <c r="D202">
+        <v>100</v>
+      </c>
+      <c r="E202">
+        <v>8.45</v>
+      </c>
+      <c r="F202" t="str">
+        <v>售价R$0-R$18.99, 重量90-100kg</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>19</v>
+      </c>
+      <c r="B203">
+        <v>48.99</v>
+      </c>
+      <c r="C203">
+        <v>90</v>
+      </c>
+      <c r="D203">
+        <v>100</v>
+      </c>
+      <c r="E203">
+        <v>12.55</v>
+      </c>
+      <c r="F203" t="str">
+        <v>售价R$19-R$48.99, 重量90-100kg</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>49</v>
+      </c>
+      <c r="B204">
+        <v>78.99</v>
+      </c>
+      <c r="C204">
+        <v>90</v>
+      </c>
+      <c r="D204">
+        <v>100</v>
+      </c>
+      <c r="E204">
+        <v>13.75</v>
+      </c>
+      <c r="F204" t="str">
+        <v>售价R$49-R$78.99, 重量90-100kg</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>79</v>
+      </c>
+      <c r="B205">
+        <v>99.99</v>
+      </c>
+      <c r="C205">
+        <v>90</v>
+      </c>
+      <c r="D205">
+        <v>100</v>
+      </c>
+      <c r="E205">
+        <v>106.55</v>
+      </c>
+      <c r="F205" t="str">
+        <v>售价R$79-R$99.99, 重量90-100kg</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>100</v>
+      </c>
+      <c r="B206">
+        <v>119.99</v>
+      </c>
+      <c r="C206">
+        <v>90</v>
+      </c>
+      <c r="D206">
+        <v>100</v>
+      </c>
+      <c r="E206">
+        <v>123.95</v>
+      </c>
+      <c r="F206" t="str">
+        <v>售价R$100-R$119.99, 重量90-100kg</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>120</v>
+      </c>
+      <c r="B207">
+        <v>149.99</v>
+      </c>
+      <c r="C207">
+        <v>90</v>
+      </c>
+      <c r="D207">
+        <v>100</v>
+      </c>
+      <c r="E207">
+        <v>139.55</v>
+      </c>
+      <c r="F207" t="str">
+        <v>售价R$120-R$149.99, 重量90-100kg</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>150</v>
+      </c>
+      <c r="B208">
+        <v>199.99</v>
+      </c>
+      <c r="C208">
+        <v>90</v>
+      </c>
+      <c r="D208">
+        <v>100</v>
+      </c>
+      <c r="E208">
+        <v>155.55</v>
+      </c>
+      <c r="F208" t="str">
+        <v>售价R$150-R$199.99, 重量90-100kg</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>200</v>
+      </c>
+      <c r="B209">
+        <v>99999</v>
+      </c>
+      <c r="C209">
+        <v>90</v>
+      </c>
+      <c r="D209">
+        <v>100</v>
+      </c>
+      <c r="E209">
+        <v>167.95</v>
+      </c>
+      <c r="F209" t="str">
+        <v>售价R$200-以上, 重量90-100kg</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>0</v>
+      </c>
+      <c r="B210">
+        <v>18.99</v>
+      </c>
+      <c r="C210">
+        <v>100</v>
+      </c>
+      <c r="D210">
+        <v>125</v>
+      </c>
+      <c r="E210">
+        <v>8.55</v>
+      </c>
+      <c r="F210" t="str">
+        <v>售价R$0-R$18.99, 重量100-125kg</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>19</v>
+      </c>
+      <c r="B211">
+        <v>48.99</v>
+      </c>
+      <c r="C211">
+        <v>100</v>
+      </c>
+      <c r="D211">
+        <v>125</v>
+      </c>
+      <c r="E211">
+        <v>12.75</v>
+      </c>
+      <c r="F211" t="str">
+        <v>售价R$19-R$48.99, 重量100-125kg</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>49</v>
+      </c>
+      <c r="B212">
+        <v>78.99</v>
+      </c>
+      <c r="C212">
+        <v>100</v>
+      </c>
+      <c r="D212">
+        <v>125</v>
+      </c>
+      <c r="E212">
+        <v>13.95</v>
+      </c>
+      <c r="F212" t="str">
+        <v>售价R$49-R$78.99, 重量100-125kg</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>79</v>
+      </c>
+      <c r="B213">
+        <v>99.99</v>
+      </c>
+      <c r="C213">
+        <v>100</v>
+      </c>
+      <c r="D213">
+        <v>125</v>
+      </c>
+      <c r="E213">
+        <v>119.25</v>
+      </c>
+      <c r="F213" t="str">
+        <v>售价R$79-R$99.99, 重量100-125kg</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>100</v>
+      </c>
+      <c r="B214">
+        <v>119.99</v>
+      </c>
+      <c r="C214">
+        <v>100</v>
+      </c>
+      <c r="D214">
+        <v>125</v>
+      </c>
+      <c r="E214">
+        <v>138.05</v>
+      </c>
+      <c r="F214" t="str">
+        <v>售价R$100-R$119.99, 重量100-125kg</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>120</v>
+      </c>
+      <c r="B215">
+        <v>149.99</v>
+      </c>
+      <c r="C215">
+        <v>100</v>
+      </c>
+      <c r="D215">
+        <v>125</v>
+      </c>
+      <c r="E215">
+        <v>156.05</v>
+      </c>
+      <c r="F215" t="str">
+        <v>售价R$120-R$149.99, 重量100-125kg</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>150</v>
+      </c>
+      <c r="B216">
+        <v>199.99</v>
+      </c>
+      <c r="C216">
+        <v>100</v>
+      </c>
+      <c r="D216">
+        <v>125</v>
+      </c>
+      <c r="E216">
+        <v>173.95</v>
+      </c>
+      <c r="F216" t="str">
+        <v>售价R$150-R$199.99, 重量100-125kg</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>200</v>
+      </c>
+      <c r="B217">
+        <v>99999</v>
+      </c>
+      <c r="C217">
+        <v>100</v>
+      </c>
+      <c r="D217">
+        <v>125</v>
+      </c>
+      <c r="E217">
+        <v>187.95</v>
+      </c>
+      <c r="F217" t="str">
+        <v>售价R$200-以上, 重量100-125kg</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>0</v>
+      </c>
+      <c r="B218">
+        <v>18.99</v>
+      </c>
+      <c r="C218">
+        <v>125</v>
+      </c>
+      <c r="D218">
+        <v>150</v>
+      </c>
+      <c r="E218">
+        <v>8.65</v>
+      </c>
+      <c r="F218" t="str">
+        <v>售价R$0-R$18.99, 重量125-150kg</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>19</v>
+      </c>
+      <c r="B219">
+        <v>48.99</v>
+      </c>
+      <c r="C219">
+        <v>125</v>
+      </c>
+      <c r="D219">
+        <v>150</v>
+      </c>
+      <c r="E219">
+        <v>12.75</v>
+      </c>
+      <c r="F219" t="str">
+        <v>售价R$19-R$48.99, 重量125-150kg</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>49</v>
+      </c>
+      <c r="B220">
+        <v>78.99</v>
+      </c>
+      <c r="C220">
+        <v>125</v>
+      </c>
+      <c r="D220">
+        <v>150</v>
+      </c>
+      <c r="E220">
+        <v>14.15</v>
+      </c>
+      <c r="F220" t="str">
+        <v>售价R$49-R$78.99, 重量125-150kg</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>79</v>
+      </c>
+      <c r="B221">
+        <v>99.99</v>
+      </c>
+      <c r="C221">
+        <v>125</v>
+      </c>
+      <c r="D221">
+        <v>150</v>
+      </c>
+      <c r="E221">
+        <v>126.55</v>
+      </c>
+      <c r="F221" t="str">
+        <v>售价R$79-R$99.99, 重量125-150kg</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>100</v>
+      </c>
+      <c r="B222">
+        <v>119.99</v>
+      </c>
+      <c r="C222">
+        <v>125</v>
+      </c>
+      <c r="D222">
+        <v>150</v>
+      </c>
+      <c r="E222">
+        <v>146.15</v>
+      </c>
+      <c r="F222" t="str">
+        <v>售价R$100-R$119.99, 重量125-150kg</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>120</v>
+      </c>
+      <c r="B223">
+        <v>149.99</v>
+      </c>
+      <c r="C223">
+        <v>125</v>
+      </c>
+      <c r="D223">
+        <v>150</v>
+      </c>
+      <c r="E223">
+        <v>165.65</v>
+      </c>
+      <c r="F223" t="str">
+        <v>售价R$120-R$149.99, 重量125-150kg</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>150</v>
+      </c>
+      <c r="B224">
+        <v>199.99</v>
+      </c>
+      <c r="C224">
+        <v>125</v>
+      </c>
+      <c r="D224">
+        <v>150</v>
+      </c>
+      <c r="E224">
+        <v>184.65</v>
+      </c>
+      <c r="F224" t="str">
+        <v>售价R$150-R$199.99, 重量125-150kg</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>200</v>
+      </c>
+      <c r="B225">
+        <v>99999</v>
+      </c>
+      <c r="C225">
+        <v>125</v>
+      </c>
+      <c r="D225">
+        <v>150</v>
+      </c>
+      <c r="E225">
+        <v>199.45</v>
+      </c>
+      <c r="F225" t="str">
+        <v>售价R$200-以上, 重量125-150kg</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>0</v>
+      </c>
+      <c r="B226">
+        <v>18.99</v>
+      </c>
+      <c r="C226">
+        <v>150</v>
+      </c>
+      <c r="D226">
+        <v>99999</v>
+      </c>
+      <c r="E226">
+        <v>8.75</v>
+      </c>
+      <c r="F226" t="str">
+        <v>售价R$0-R$18.99, 重量150-kg以上</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>19</v>
+      </c>
+      <c r="B227">
+        <v>48.99</v>
+      </c>
+      <c r="C227">
+        <v>150</v>
+      </c>
+      <c r="D227">
+        <v>99999</v>
+      </c>
+      <c r="E227">
+        <v>12.95</v>
+      </c>
+      <c r="F227" t="str">
+        <v>售价R$19-R$48.99, 重量150-kg以上</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>49</v>
+      </c>
+      <c r="B228">
+        <v>78.99</v>
+      </c>
+      <c r="C228">
+        <v>150</v>
+      </c>
+      <c r="D228">
+        <v>99999</v>
+      </c>
+      <c r="E228">
+        <v>14.35</v>
+      </c>
+      <c r="F228" t="str">
+        <v>售价R$49-R$78.99, 重量150-kg以上</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>79</v>
+      </c>
+      <c r="B229">
+        <v>99.99</v>
+      </c>
+      <c r="C229">
+        <v>150</v>
+      </c>
+      <c r="D229">
+        <v>99999</v>
+      </c>
+      <c r="E229">
+        <v>166.15</v>
+      </c>
+      <c r="F229" t="str">
+        <v>售价R$79-R$99.99, 重量150-kg以上</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>100</v>
+      </c>
+      <c r="B230">
+        <v>119.99</v>
+      </c>
+      <c r="C230">
+        <v>150</v>
+      </c>
+      <c r="D230">
+        <v>99999</v>
+      </c>
+      <c r="E230">
+        <v>192.45</v>
+      </c>
+      <c r="F230" t="str">
+        <v>售价R$100-R$119.99, 重量150-kg以上</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>120</v>
+      </c>
+      <c r="B231">
+        <v>149.99</v>
+      </c>
+      <c r="C231">
+        <v>150</v>
+      </c>
+      <c r="D231">
+        <v>99999</v>
+      </c>
+      <c r="E231">
+        <v>217.55</v>
+      </c>
+      <c r="F231" t="str">
+        <v>售价R$120-R$149.99, 重量150-kg以上</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>150</v>
+      </c>
+      <c r="B232">
+        <v>199.99</v>
+      </c>
+      <c r="C232">
+        <v>150</v>
+      </c>
+      <c r="D232">
+        <v>99999</v>
+      </c>
+      <c r="E232">
+        <v>242.55</v>
+      </c>
+      <c r="F232" t="str">
+        <v>售价R$150-R$199.99, 重量150-kg以上</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>200</v>
+      </c>
+      <c r="B233">
+        <v>99999</v>
+      </c>
+      <c r="C233">
+        <v>150</v>
+      </c>
+      <c r="D233">
+        <v>99999</v>
+      </c>
+      <c r="E233">
+        <v>261.95</v>
+      </c>
+      <c r="F233" t="str">
+        <v>售价R$200-以上, 重量150-kg以上</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F233"/>
   </ignoredErrors>
 </worksheet>
 </file>
